--- a/knowledge/proprietary/_metadata.xlsx
+++ b/knowledge/proprietary/_metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/charnould/GitHub/pierre/knowledge/proprietary/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CD1E346-E8E6-744D-8531-A8A2305D2F63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89E5C6C6-8EDD-1F46-8E99-AD535C78E0CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2740" yWindow="1420" windowWidth="27500" windowHeight="17400" xr2:uid="{E5B0FB10-8797-D243-A0FA-6D923D5CC0EA}"/>
   </bookViews>
@@ -16,9 +16,9 @@
     <sheet name="metadata" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">metadata!$A$2:$E$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">metadata!$A$2:$G$2</definedName>
   </definedNames>
-  <calcPr calcId="181029" calcOnSave="0"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="24">
   <si>
     <t>test-markdown-file.md</t>
   </si>
@@ -157,24 +157,30 @@
   <si>
     <t>Ci-après les noms des agents et cadre d'astreinte pour la semaine considérée chez Pierre Habitat :</t>
   </si>
+  <si>
+    <t>Colonne de l'entité</t>
+  </si>
+  <si>
+    <t>Type de l'entité</t>
+  </si>
+  <si>
+    <t>Building</t>
+  </si>
+  <si>
+    <t>Process</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -237,21 +243,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
   </cellXfs>
@@ -588,164 +591,174 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F3359B2-613C-1246-BB58-A3F329ACACAC}">
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="20" customHeight="1" outlineLevelRow="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="22.1640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="29.83203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.1640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.5" style="1" customWidth="1"/>
     <col min="5" max="5" width="101.33203125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="10.83203125" style="1"/>
+    <col min="6" max="6" width="11.5" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.1640625" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="5" customFormat="1" ht="78" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:7" s="4" customFormat="1" ht="98" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:7" ht="76" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+      <c r="F2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="1">
         <v>1</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="1">
         <v>3</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
+      <c r="F3" s="1">
         <v>1</v>
       </c>
-      <c r="B4" s="2">
+      <c r="G3" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1">
         <v>2</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="1">
         <v>1</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="1">
         <v>3</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="1">
         <v>1</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
+      <c r="F5" s="1">
+        <v>4</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="1">
         <v>1</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="1">
         <v>5</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="1">
         <v>2</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="1">
         <v>5</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
+    </row>
+    <row r="9" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E9" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:E2" xr:uid="{0F3359B2-613C-1246-BB58-A3F329ACACAC}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:E6">
-      <sortCondition ref="D2:D6"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A2:G2" xr:uid="{0F3359B2-613C-1246-BB58-A3F329ACACAC}"/>
   <dataConsolidate/>
   <dataValidations count="2">
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C204" xr:uid="{49006576-7484-B84D-A51B-69FE1DA1041A}">
